--- a/mosip_master/xlsx/applicant_valid_document.xlsx
+++ b/mosip_master/xlsx/applicant_valid_document.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NIRA-DEV\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nira-registration\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39506D7E-1CDD-45F8-B2FB-3B2FB087B262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD8571A-7956-40B9-B4EF-CC75BF428BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{E643BBC9-814E-45CC-B262-943720784A73}"/>
   </bookViews>
   <sheets>
     <sheet name="applicant_valid_document" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">applicant_valid_document!$A$1:$K$422</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2923" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2944" uniqueCount="153">
   <si>
     <t>apptyp_code</t>
   </si>
@@ -468,6 +471,30 @@
   </si>
   <si>
     <t>'800</t>
+  </si>
+  <si>
+    <t>035</t>
+  </si>
+  <si>
+    <t>PODMG</t>
+  </si>
+  <si>
+    <t>DMG</t>
+  </si>
+  <si>
+    <t>NID</t>
+  </si>
+  <si>
+    <t>POLCL</t>
+  </si>
+  <si>
+    <t>LCL</t>
+  </si>
+  <si>
+    <t>LFCV</t>
+  </si>
+  <si>
+    <t>RECLET</t>
   </si>
 </sst>
 </file>
@@ -1330,6 +1357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{789F9386-0150-4488-A6FA-8417165A0826}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K433"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1374,7 +1402,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>89</v>
       </c>
@@ -1400,7 +1428,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -1426,7 +1454,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>89</v>
       </c>
@@ -1452,7 +1480,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>90</v>
       </c>
@@ -1478,7 +1506,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>90</v>
       </c>
@@ -1504,7 +1532,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>90</v>
       </c>
@@ -1530,7 +1558,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>90</v>
       </c>
@@ -1556,7 +1584,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>90</v>
       </c>
@@ -1582,12 +1610,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>91</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>148</v>
       </c>
       <c r="C10" t="s">
         <v>55</v>
@@ -1608,7 +1636,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>91</v>
       </c>
@@ -1634,7 +1662,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>91</v>
       </c>
@@ -1660,7 +1688,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>91</v>
       </c>
@@ -1686,7 +1714,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -1712,7 +1740,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>92</v>
       </c>
@@ -1738,7 +1766,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>92</v>
       </c>
@@ -1764,7 +1792,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>92</v>
       </c>
@@ -1790,7 +1818,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -1816,7 +1844,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>92</v>
       </c>
@@ -1842,7 +1870,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>92</v>
       </c>
@@ -1868,7 +1896,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>93</v>
       </c>
@@ -1894,7 +1922,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>93</v>
       </c>
@@ -1920,7 +1948,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>93</v>
       </c>
@@ -1946,7 +1974,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>93</v>
       </c>
@@ -1972,7 +2000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>93</v>
       </c>
@@ -1998,7 +2026,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>93</v>
       </c>
@@ -2024,7 +2052,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>93</v>
       </c>
@@ -2050,7 +2078,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>93</v>
       </c>
@@ -2076,7 +2104,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>93</v>
       </c>
@@ -2102,7 +2130,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>93</v>
       </c>
@@ -2128,7 +2156,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>94</v>
       </c>
@@ -2154,7 +2182,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>94</v>
       </c>
@@ -2180,7 +2208,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>94</v>
       </c>
@@ -2206,7 +2234,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>94</v>
       </c>
@@ -2232,7 +2260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>94</v>
       </c>
@@ -2258,7 +2286,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>95</v>
       </c>
@@ -2284,7 +2312,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>95</v>
       </c>
@@ -2310,7 +2338,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>95</v>
       </c>
@@ -2336,7 +2364,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>95</v>
       </c>
@@ -2362,7 +2390,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>95</v>
       </c>
@@ -2388,7 +2416,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>95</v>
       </c>
@@ -2414,7 +2442,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>95</v>
       </c>
@@ -2440,7 +2468,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>96</v>
       </c>
@@ -2466,7 +2494,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>96</v>
       </c>
@@ -2492,7 +2520,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>96</v>
       </c>
@@ -2518,7 +2546,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>96</v>
       </c>
@@ -2544,7 +2572,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>96</v>
       </c>
@@ -2570,7 +2598,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>97</v>
       </c>
@@ -2596,7 +2624,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>97</v>
       </c>
@@ -2622,7 +2650,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>97</v>
       </c>
@@ -2648,7 +2676,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>97</v>
       </c>
@@ -2674,7 +2702,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>97</v>
       </c>
@@ -2700,7 +2728,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>97</v>
       </c>
@@ -2726,7 +2754,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>97</v>
       </c>
@@ -2752,7 +2780,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>98</v>
       </c>
@@ -2778,7 +2806,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>98</v>
       </c>
@@ -2804,7 +2832,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>98</v>
       </c>
@@ -2830,7 +2858,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>99</v>
       </c>
@@ -2856,7 +2884,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>99</v>
       </c>
@@ -2882,7 +2910,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>99</v>
       </c>
@@ -2908,7 +2936,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>99</v>
       </c>
@@ -2934,7 +2962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>99</v>
       </c>
@@ -2960,7 +2988,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>99</v>
       </c>
@@ -2986,7 +3014,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -3012,7 +3040,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>100</v>
       </c>
@@ -3038,7 +3066,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>100</v>
       </c>
@@ -3064,7 +3092,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>100</v>
       </c>
@@ -3090,7 +3118,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>100</v>
       </c>
@@ -3116,7 +3144,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>101</v>
       </c>
@@ -3142,7 +3170,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>101</v>
       </c>
@@ -3168,7 +3196,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>101</v>
       </c>
@@ -3194,7 +3222,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>101</v>
       </c>
@@ -3220,7 +3248,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>101</v>
       </c>
@@ -3246,7 +3274,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>101</v>
       </c>
@@ -3272,7 +3300,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>101</v>
       </c>
@@ -3298,7 +3326,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>101</v>
       </c>
@@ -3324,7 +3352,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>102</v>
       </c>
@@ -3350,7 +3378,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>102</v>
       </c>
@@ -3376,7 +3404,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>102</v>
       </c>
@@ -3402,7 +3430,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>103</v>
       </c>
@@ -3428,7 +3456,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>103</v>
       </c>
@@ -3454,7 +3482,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>103</v>
       </c>
@@ -3480,7 +3508,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>103</v>
       </c>
@@ -3506,7 +3534,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>103</v>
       </c>
@@ -3532,7 +3560,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>103</v>
       </c>
@@ -3558,7 +3586,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>104</v>
       </c>
@@ -3584,7 +3612,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>104</v>
       </c>
@@ -3610,7 +3638,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>104</v>
       </c>
@@ -3636,7 +3664,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>104</v>
       </c>
@@ -3662,7 +3690,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>104</v>
       </c>
@@ -3688,7 +3716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>105</v>
       </c>
@@ -3714,7 +3742,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>105</v>
       </c>
@@ -3740,7 +3768,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>105</v>
       </c>
@@ -3766,7 +3794,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>105</v>
       </c>
@@ -3792,7 +3820,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>105</v>
       </c>
@@ -3818,7 +3846,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>105</v>
       </c>
@@ -3844,7 +3872,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>105</v>
       </c>
@@ -3870,7 +3898,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>105</v>
       </c>
@@ -3896,7 +3924,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>106</v>
       </c>
@@ -3922,7 +3950,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>106</v>
       </c>
@@ -3948,7 +3976,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>106</v>
       </c>
@@ -3974,7 +4002,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>106</v>
       </c>
@@ -4000,7 +4028,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>107</v>
       </c>
@@ -4026,7 +4054,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>107</v>
       </c>
@@ -4052,7 +4080,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>107</v>
       </c>
@@ -4078,7 +4106,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>107</v>
       </c>
@@ -4104,7 +4132,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>107</v>
       </c>
@@ -4130,7 +4158,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>108</v>
       </c>
@@ -4156,7 +4184,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>108</v>
       </c>
@@ -4182,7 +4210,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>108</v>
       </c>
@@ -4208,7 +4236,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>108</v>
       </c>
@@ -4234,7 +4262,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>108</v>
       </c>
@@ -4260,7 +4288,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>108</v>
       </c>
@@ -4286,7 +4314,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>109</v>
       </c>
@@ -4312,7 +4340,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>109</v>
       </c>
@@ -4338,7 +4366,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>109</v>
       </c>
@@ -4364,7 +4392,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>109</v>
       </c>
@@ -4390,7 +4418,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>109</v>
       </c>
@@ -4416,7 +4444,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>109</v>
       </c>
@@ -4442,7 +4470,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>109</v>
       </c>
@@ -4468,7 +4496,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>109</v>
       </c>
@@ -4494,7 +4522,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>110</v>
       </c>
@@ -4520,7 +4548,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>110</v>
       </c>
@@ -4546,7 +4574,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>110</v>
       </c>
@@ -4572,7 +4600,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>110</v>
       </c>
@@ -4598,7 +4626,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>110</v>
       </c>
@@ -4624,7 +4652,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>110</v>
       </c>
@@ -4650,7 +4678,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>110</v>
       </c>
@@ -4676,7 +4704,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>110</v>
       </c>
@@ -4702,7 +4730,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>111</v>
       </c>
@@ -4728,7 +4756,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>111</v>
       </c>
@@ -4754,7 +4782,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>111</v>
       </c>
@@ -4780,7 +4808,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>111</v>
       </c>
@@ -4806,7 +4834,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>111</v>
       </c>
@@ -4832,7 +4860,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>111</v>
       </c>
@@ -4858,7 +4886,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>111</v>
       </c>
@@ -4884,7 +4912,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>111</v>
       </c>
@@ -4910,7 +4938,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>112</v>
       </c>
@@ -4936,7 +4964,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>112</v>
       </c>
@@ -4962,7 +4990,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>112</v>
       </c>
@@ -4988,7 +5016,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>112</v>
       </c>
@@ -5014,7 +5042,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>112</v>
       </c>
@@ -5040,7 +5068,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>112</v>
       </c>
@@ -5066,7 +5094,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>112</v>
       </c>
@@ -5092,7 +5120,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>112</v>
       </c>
@@ -5118,7 +5146,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>113</v>
       </c>
@@ -5144,7 +5172,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>113</v>
       </c>
@@ -5170,7 +5198,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>113</v>
       </c>
@@ -5196,7 +5224,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>113</v>
       </c>
@@ -5222,7 +5250,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>113</v>
       </c>
@@ -5248,7 +5276,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>113</v>
       </c>
@@ -5274,7 +5302,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>113</v>
       </c>
@@ -5300,7 +5328,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>113</v>
       </c>
@@ -5326,7 +5354,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>113</v>
       </c>
@@ -5352,7 +5380,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>113</v>
       </c>
@@ -5378,7 +5406,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>113</v>
       </c>
@@ -5404,7 +5432,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>113</v>
       </c>
@@ -5430,7 +5458,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>114</v>
       </c>
@@ -5456,7 +5484,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>114</v>
       </c>
@@ -5482,7 +5510,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>114</v>
       </c>
@@ -5508,7 +5536,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>114</v>
       </c>
@@ -5534,7 +5562,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>114</v>
       </c>
@@ -5560,7 +5588,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>114</v>
       </c>
@@ -5586,7 +5614,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>114</v>
       </c>
@@ -5612,7 +5640,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>114</v>
       </c>
@@ -5638,7 +5666,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>115</v>
       </c>
@@ -5664,7 +5692,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>115</v>
       </c>
@@ -5690,7 +5718,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>115</v>
       </c>
@@ -5716,7 +5744,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>115</v>
       </c>
@@ -5742,7 +5770,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>115</v>
       </c>
@@ -5768,7 +5796,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>115</v>
       </c>
@@ -5794,7 +5822,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>115</v>
       </c>
@@ -5820,7 +5848,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>115</v>
       </c>
@@ -5846,7 +5874,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>116</v>
       </c>
@@ -5872,7 +5900,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>116</v>
       </c>
@@ -5898,7 +5926,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>116</v>
       </c>
@@ -5924,7 +5952,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>116</v>
       </c>
@@ -5950,7 +5978,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>116</v>
       </c>
@@ -5976,7 +6004,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>116</v>
       </c>
@@ -6002,7 +6030,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>116</v>
       </c>
@@ -6028,7 +6056,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>116</v>
       </c>
@@ -6054,7 +6082,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>116</v>
       </c>
@@ -6080,7 +6108,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>117</v>
       </c>
@@ -6106,7 +6134,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>117</v>
       </c>
@@ -6132,7 +6160,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>117</v>
       </c>
@@ -6158,7 +6186,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>117</v>
       </c>
@@ -6184,7 +6212,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>117</v>
       </c>
@@ -6210,7 +6238,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>117</v>
       </c>
@@ -6236,7 +6264,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>117</v>
       </c>
@@ -6262,7 +6290,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>117</v>
       </c>
@@ -6288,7 +6316,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>117</v>
       </c>
@@ -6314,7 +6342,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>118</v>
       </c>
@@ -6340,7 +6368,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>118</v>
       </c>
@@ -6366,7 +6394,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>118</v>
       </c>
@@ -6392,7 +6420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>118</v>
       </c>
@@ -6418,7 +6446,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>118</v>
       </c>
@@ -6444,7 +6472,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>118</v>
       </c>
@@ -6470,7 +6498,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>118</v>
       </c>
@@ -6496,7 +6524,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>118</v>
       </c>
@@ -6522,7 +6550,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>118</v>
       </c>
@@ -6548,7 +6576,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>119</v>
       </c>
@@ -6574,7 +6602,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>119</v>
       </c>
@@ -6600,7 +6628,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>119</v>
       </c>
@@ -6626,7 +6654,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>119</v>
       </c>
@@ -6652,7 +6680,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>119</v>
       </c>
@@ -6678,7 +6706,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>119</v>
       </c>
@@ -6704,7 +6732,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>119</v>
       </c>
@@ -6730,7 +6758,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>119</v>
       </c>
@@ -6756,7 +6784,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>119</v>
       </c>
@@ -6782,7 +6810,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>120</v>
       </c>
@@ -6808,7 +6836,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>120</v>
       </c>
@@ -6834,7 +6862,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>120</v>
       </c>
@@ -6860,7 +6888,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>120</v>
       </c>
@@ -6886,7 +6914,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>120</v>
       </c>
@@ -6912,7 +6940,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>120</v>
       </c>
@@ -6938,7 +6966,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>120</v>
       </c>
@@ -6964,7 +6992,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>120</v>
       </c>
@@ -6990,7 +7018,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>120</v>
       </c>
@@ -7016,7 +7044,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>121</v>
       </c>
@@ -7042,7 +7070,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>121</v>
       </c>
@@ -7068,7 +7096,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>121</v>
       </c>
@@ -7094,7 +7122,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>121</v>
       </c>
@@ -7120,7 +7148,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>121</v>
       </c>
@@ -7146,7 +7174,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>121</v>
       </c>
@@ -7172,7 +7200,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>121</v>
       </c>
@@ -7198,7 +7226,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>121</v>
       </c>
@@ -7224,7 +7252,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>121</v>
       </c>
@@ -7250,7 +7278,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>122</v>
       </c>
@@ -7276,7 +7304,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>122</v>
       </c>
@@ -7302,7 +7330,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>122</v>
       </c>
@@ -7328,7 +7356,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>123</v>
       </c>
@@ -7354,7 +7382,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>123</v>
       </c>
@@ -7380,7 +7408,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>124</v>
       </c>
@@ -7406,7 +7434,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>124</v>
       </c>
@@ -7432,7 +7460,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>124</v>
       </c>
@@ -7458,7 +7486,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>124</v>
       </c>
@@ -7484,7 +7512,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>124</v>
       </c>
@@ -7510,7 +7538,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>124</v>
       </c>
@@ -7536,7 +7564,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>124</v>
       </c>
@@ -7562,7 +7590,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>124</v>
       </c>
@@ -7588,7 +7616,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>124</v>
       </c>
@@ -7614,7 +7642,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>124</v>
       </c>
@@ -7640,7 +7668,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>124</v>
       </c>
@@ -7666,7 +7694,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>124</v>
       </c>
@@ -7692,7 +7720,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>124</v>
       </c>
@@ -7718,7 +7746,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>125</v>
       </c>
@@ -7744,7 +7772,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>125</v>
       </c>
@@ -7770,7 +7798,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>125</v>
       </c>
@@ -7796,7 +7824,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>125</v>
       </c>
@@ -7822,7 +7850,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>125</v>
       </c>
@@ -7848,7 +7876,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>125</v>
       </c>
@@ -7874,7 +7902,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>125</v>
       </c>
@@ -7900,7 +7928,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>125</v>
       </c>
@@ -7926,7 +7954,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>125</v>
       </c>
@@ -7952,7 +7980,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>125</v>
       </c>
@@ -7978,7 +8006,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>126</v>
       </c>
@@ -8004,7 +8032,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>126</v>
       </c>
@@ -8030,7 +8058,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>126</v>
       </c>
@@ -8056,7 +8084,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>126</v>
       </c>
@@ -8082,7 +8110,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>126</v>
       </c>
@@ -8108,7 +8136,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>126</v>
       </c>
@@ -8134,7 +8162,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>126</v>
       </c>
@@ -8160,7 +8188,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>127</v>
       </c>
@@ -8186,7 +8214,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>127</v>
       </c>
@@ -8212,7 +8240,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>127</v>
       </c>
@@ -8238,7 +8266,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>127</v>
       </c>
@@ -8264,7 +8292,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>127</v>
       </c>
@@ -8290,7 +8318,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>127</v>
       </c>
@@ -8316,7 +8344,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>127</v>
       </c>
@@ -8342,7 +8370,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>128</v>
       </c>
@@ -8368,7 +8396,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>128</v>
       </c>
@@ -8394,7 +8422,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>128</v>
       </c>
@@ -8420,7 +8448,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>128</v>
       </c>
@@ -8446,7 +8474,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>128</v>
       </c>
@@ -8472,7 +8500,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>128</v>
       </c>
@@ -8498,7 +8526,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>128</v>
       </c>
@@ -8524,7 +8552,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>128</v>
       </c>
@@ -8550,7 +8578,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>128</v>
       </c>
@@ -8576,7 +8604,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>128</v>
       </c>
@@ -8602,7 +8630,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>128</v>
       </c>
@@ -8628,7 +8656,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>129</v>
       </c>
@@ -8654,7 +8682,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>129</v>
       </c>
@@ -8680,7 +8708,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>129</v>
       </c>
@@ -8706,7 +8734,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>129</v>
       </c>
@@ -8732,7 +8760,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>129</v>
       </c>
@@ -8758,7 +8786,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>129</v>
       </c>
@@ -8784,7 +8812,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>129</v>
       </c>
@@ -8810,7 +8838,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>129</v>
       </c>
@@ -8836,7 +8864,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>129</v>
       </c>
@@ -8862,7 +8890,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>129</v>
       </c>
@@ -8888,7 +8916,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>129</v>
       </c>
@@ -8914,7 +8942,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>129</v>
       </c>
@@ -8940,7 +8968,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>130</v>
       </c>
@@ -8966,7 +8994,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>130</v>
       </c>
@@ -8992,7 +9020,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>130</v>
       </c>
@@ -9018,7 +9046,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>130</v>
       </c>
@@ -9044,7 +9072,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>130</v>
       </c>
@@ -9070,7 +9098,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>130</v>
       </c>
@@ -9096,7 +9124,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>130</v>
       </c>
@@ -9122,7 +9150,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>130</v>
       </c>
@@ -9148,7 +9176,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>130</v>
       </c>
@@ -9174,7 +9202,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>130</v>
       </c>
@@ -9200,7 +9228,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>130</v>
       </c>
@@ -9226,7 +9254,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>131</v>
       </c>
@@ -9252,7 +9280,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>131</v>
       </c>
@@ -9278,7 +9306,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>131</v>
       </c>
@@ -9304,7 +9332,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>131</v>
       </c>
@@ -9330,7 +9358,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>131</v>
       </c>
@@ -9356,7 +9384,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>131</v>
       </c>
@@ -9382,7 +9410,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>131</v>
       </c>
@@ -9408,7 +9436,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>131</v>
       </c>
@@ -9434,7 +9462,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>131</v>
       </c>
@@ -9460,7 +9488,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>131</v>
       </c>
@@ -9486,7 +9514,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>131</v>
       </c>
@@ -9512,7 +9540,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>131</v>
       </c>
@@ -9538,7 +9566,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>131</v>
       </c>
@@ -9564,7 +9592,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>131</v>
       </c>
@@ -9590,7 +9618,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>132</v>
       </c>
@@ -9616,7 +9644,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>132</v>
       </c>
@@ -9642,7 +9670,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>132</v>
       </c>
@@ -9668,7 +9696,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>132</v>
       </c>
@@ -9694,7 +9722,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>132</v>
       </c>
@@ -9720,7 +9748,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>132</v>
       </c>
@@ -9746,7 +9774,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>132</v>
       </c>
@@ -9772,7 +9800,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>132</v>
       </c>
@@ -9798,7 +9826,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>132</v>
       </c>
@@ -9824,7 +9852,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>132</v>
       </c>
@@ -9850,7 +9878,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>132</v>
       </c>
@@ -9876,7 +9904,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>133</v>
       </c>
@@ -9902,7 +9930,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>133</v>
       </c>
@@ -9928,7 +9956,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>133</v>
       </c>
@@ -9954,7 +9982,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>133</v>
       </c>
@@ -9980,7 +10008,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>134</v>
       </c>
@@ -10006,7 +10034,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>134</v>
       </c>
@@ -10032,7 +10060,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>134</v>
       </c>
@@ -10058,7 +10086,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>134</v>
       </c>
@@ -10084,7 +10112,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>134</v>
       </c>
@@ -10110,7 +10138,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>134</v>
       </c>
@@ -10136,7 +10164,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>135</v>
       </c>
@@ -10162,7 +10190,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>135</v>
       </c>
@@ -10188,7 +10216,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>135</v>
       </c>
@@ -10214,7 +10242,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>135</v>
       </c>
@@ -10240,7 +10268,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>135</v>
       </c>
@@ -10266,83 +10294,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A344" t="s">
-        <v>136</v>
-      </c>
-      <c r="B344" t="s">
-        <v>58</v>
-      </c>
-      <c r="C344" t="s">
-        <v>75</v>
-      </c>
-      <c r="D344" t="s">
-        <v>12</v>
-      </c>
-      <c r="E344" t="s">
-        <v>13</v>
-      </c>
-      <c r="F344" t="s">
-        <v>14</v>
-      </c>
-      <c r="G344" s="2">
-        <v>45516.752083333333</v>
-      </c>
-      <c r="J344" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A345" t="s">
-        <v>136</v>
-      </c>
-      <c r="B345" t="s">
-        <v>58</v>
-      </c>
-      <c r="C345" t="s">
-        <v>59</v>
-      </c>
-      <c r="D345" t="s">
-        <v>12</v>
-      </c>
-      <c r="E345" t="s">
-        <v>13</v>
-      </c>
-      <c r="F345" t="s">
-        <v>14</v>
-      </c>
-      <c r="G345" s="2">
-        <v>45516.752083333333</v>
-      </c>
-      <c r="J345" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A346" t="s">
-        <v>136</v>
-      </c>
-      <c r="B346" t="s">
-        <v>58</v>
-      </c>
-      <c r="C346" t="s">
-        <v>29</v>
-      </c>
-      <c r="D346" t="s">
-        <v>12</v>
-      </c>
-      <c r="E346" t="s">
-        <v>13</v>
-      </c>
-      <c r="F346" t="s">
-        <v>14</v>
-      </c>
-      <c r="G346" s="2">
-        <v>45516.752083333333</v>
-      </c>
-      <c r="J346" t="s">
-        <v>15</v>
-      </c>
+    <row r="344" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G344" s="2"/>
+    </row>
+    <row r="345" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G345" s="2"/>
+    </row>
+    <row r="346" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G346" s="2"/>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
@@ -10404,7 +10363,7 @@
         <v>58</v>
       </c>
       <c r="C349" t="s">
-        <v>60</v>
+        <v>151</v>
       </c>
       <c r="D349" t="s">
         <v>12</v>
@@ -10534,7 +10493,7 @@
         <v>58</v>
       </c>
       <c r="C354" t="s">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="D354" t="s">
         <v>12</v>
@@ -10578,7 +10537,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>137</v>
       </c>
@@ -10604,7 +10563,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>137</v>
       </c>
@@ -10630,7 +10589,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>137</v>
       </c>
@@ -10656,7 +10615,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>137</v>
       </c>
@@ -10682,7 +10641,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>137</v>
       </c>
@@ -10708,7 +10667,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>137</v>
       </c>
@@ -10734,7 +10693,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>137</v>
       </c>
@@ -10760,7 +10719,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>137</v>
       </c>
@@ -10786,7 +10745,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>137</v>
       </c>
@@ -10812,7 +10771,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>137</v>
       </c>
@@ -10838,7 +10797,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>137</v>
       </c>
@@ -10864,7 +10823,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>138</v>
       </c>
@@ -10890,7 +10849,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>138</v>
       </c>
@@ -10916,7 +10875,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>138</v>
       </c>
@@ -10942,7 +10901,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>138</v>
       </c>
@@ -10968,7 +10927,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>138</v>
       </c>
@@ -10994,7 +10953,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>138</v>
       </c>
@@ -11020,7 +10979,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>138</v>
       </c>
@@ -11046,7 +11005,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>138</v>
       </c>
@@ -11072,7 +11031,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>138</v>
       </c>
@@ -11098,7 +11057,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>139</v>
       </c>
@@ -11124,7 +11083,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>139</v>
       </c>
@@ -11150,7 +11109,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>139</v>
       </c>
@@ -11176,7 +11135,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>139</v>
       </c>
@@ -11202,7 +11161,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>139</v>
       </c>
@@ -11228,7 +11187,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>140</v>
       </c>
@@ -11254,7 +11213,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>140</v>
       </c>
@@ -11280,7 +11239,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>140</v>
       </c>
@@ -11306,7 +11265,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>140</v>
       </c>
@@ -11332,7 +11291,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>140</v>
       </c>
@@ -11358,7 +11317,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>141</v>
       </c>
@@ -11384,7 +11343,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>141</v>
       </c>
@@ -11410,7 +11369,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>141</v>
       </c>
@@ -11436,7 +11395,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>141</v>
       </c>
@@ -11462,7 +11421,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>141</v>
       </c>
@@ -11488,7 +11447,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>141</v>
       </c>
@@ -11514,7 +11473,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>141</v>
       </c>
@@ -11540,7 +11499,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>142</v>
       </c>
@@ -11566,7 +11525,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>142</v>
       </c>
@@ -11592,7 +11551,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>142</v>
       </c>
@@ -11618,7 +11577,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>142</v>
       </c>
@@ -11644,7 +11603,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>142</v>
       </c>
@@ -11670,7 +11629,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>142</v>
       </c>
@@ -11696,7 +11655,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>142</v>
       </c>
@@ -11722,7 +11681,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>142</v>
       </c>
@@ -11748,7 +11707,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>142</v>
       </c>
@@ -11774,7 +11733,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>142</v>
       </c>
@@ -11800,7 +11759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>142</v>
       </c>
@@ -11826,7 +11785,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>143</v>
       </c>
@@ -11852,7 +11811,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>143</v>
       </c>
@@ -11878,7 +11837,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>144</v>
       </c>
@@ -11904,7 +11863,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>144</v>
       </c>
@@ -11930,7 +11889,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>144</v>
       </c>
@@ -11956,7 +11915,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>144</v>
       </c>
@@ -11982,7 +11941,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>144</v>
       </c>
@@ -12008,7 +11967,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>144</v>
       </c>
@@ -12034,7 +11993,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>144</v>
       </c>
@@ -12060,7 +12019,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>144</v>
       </c>
@@ -12086,7 +12045,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>144</v>
       </c>
@@ -12112,7 +12071,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>144</v>
       </c>
@@ -12138,7 +12097,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>144</v>
       </c>
@@ -12164,7 +12123,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>144</v>
       </c>
@@ -12190,29 +12149,161 @@
         <v>15</v>
       </c>
     </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A418" s="1"/>
-      <c r="G418" s="2"/>
-    </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A419" s="1"/>
-      <c r="G419" s="2"/>
-    </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A420" s="1"/>
-      <c r="G420" s="2"/>
-    </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A421" s="1"/>
-      <c r="G421" s="2"/>
-    </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A422" s="1"/>
-      <c r="G422" s="2"/>
+    <row r="418" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A418" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B418" t="s">
+        <v>148</v>
+      </c>
+      <c r="C418" t="s">
+        <v>55</v>
+      </c>
+      <c r="D418" t="s">
+        <v>12</v>
+      </c>
+      <c r="E418" t="s">
+        <v>13</v>
+      </c>
+      <c r="F418" t="s">
+        <v>14</v>
+      </c>
+      <c r="G418" s="2">
+        <v>45516.752083333333</v>
+      </c>
+      <c r="J418" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="419" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A419" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B419" t="s">
+        <v>146</v>
+      </c>
+      <c r="C419" t="s">
+        <v>147</v>
+      </c>
+      <c r="D419" t="s">
+        <v>12</v>
+      </c>
+      <c r="E419" t="s">
+        <v>13</v>
+      </c>
+      <c r="F419" t="s">
+        <v>14</v>
+      </c>
+      <c r="G419" s="2">
+        <v>45516.752083333333</v>
+      </c>
+      <c r="J419" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="420" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A420" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B420" t="s">
+        <v>82</v>
+      </c>
+      <c r="C420" t="s">
+        <v>20</v>
+      </c>
+      <c r="D420" t="s">
+        <v>12</v>
+      </c>
+      <c r="E420" t="s">
+        <v>13</v>
+      </c>
+      <c r="F420" t="s">
+        <v>14</v>
+      </c>
+      <c r="G420" s="2">
+        <v>45516.752083333333</v>
+      </c>
+      <c r="J420" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="421" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A421" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B421" t="s">
+        <v>53</v>
+      </c>
+      <c r="C421" t="s">
+        <v>54</v>
+      </c>
+      <c r="D421" t="s">
+        <v>12</v>
+      </c>
+      <c r="E421" t="s">
+        <v>13</v>
+      </c>
+      <c r="F421" t="s">
+        <v>14</v>
+      </c>
+      <c r="G421" s="2">
+        <v>45516.752083333333</v>
+      </c>
+      <c r="J421" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="422" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A422" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B422" t="s">
+        <v>21</v>
+      </c>
+      <c r="C422" t="s">
+        <v>22</v>
+      </c>
+      <c r="D422" t="s">
+        <v>12</v>
+      </c>
+      <c r="E422" t="s">
+        <v>13</v>
+      </c>
+      <c r="F422" t="s">
+        <v>14</v>
+      </c>
+      <c r="G422" s="2">
+        <v>45516.752083333333</v>
+      </c>
+      <c r="J422" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="423" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A423" s="1"/>
-      <c r="G423" s="2"/>
+      <c r="A423" t="s">
+        <v>136</v>
+      </c>
+      <c r="B423" t="s">
+        <v>149</v>
+      </c>
+      <c r="C423" t="s">
+        <v>150</v>
+      </c>
+      <c r="D423" t="s">
+        <v>12</v>
+      </c>
+      <c r="E423" t="s">
+        <v>13</v>
+      </c>
+      <c r="F423" t="s">
+        <v>14</v>
+      </c>
+      <c r="G423" s="2">
+        <v>45674.752083333333</v>
+      </c>
+      <c r="J423" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="424" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A424" s="1"/>
@@ -12255,6 +12346,13 @@
       <c r="G433" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K422" xr:uid="{789F9386-0150-4488-A6FA-8417165A0826}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="'705"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId1"/>
 </worksheet>
